--- a/docs/works/api-spec-2026-02-10.xlsx
+++ b/docs/works/api-spec-2026-02-10.xlsx
@@ -3045,13 +3045,7 @@
           <t>Request Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "+0gvit7igCOB2BwzFRDFGGZ779xO8Ha6BtWSL4XJDeOp/piL2v5rlkvznXX6ld3sEU7LR8Pp6JYOvBYg5dO10QJLWPBNODCLkbEf5B0AHI8RrtgzKtSBfmEjnvKvL3+rTfKj5RDUEIZRIIy0OJRAldMMu5mc3TfEKN9vCIW7WDutx7AIXhL8H9zcPeLZA1WLYCBoQjJS75Btn8yorDfzrI8hYwX7il3dqtkoYCVnGjggkouVt03Up+YaNZ2aIQurkPAelt9kZFtAe1hQZBuEJudSpL3PC9yH1y74T7TgxuwX60PcoyDHNTlIYivze7nwB6QKbYZfrQzwV3mpT/LpL+oo2QsIO4SI0WvdSx3EdRVpZH3GUnvvQoEDued4eAITeLzAJSWsGuY7fWThWUA+mnknmO5MySABRZw2H9vpobib7dzKwZBo/ttM2gIKrKO9"
-}</t>
-        </is>
-      </c>
+      <c r="B10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -3076,13 +3070,7 @@
           <t>Response Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "G95WBgtt2l8EkUe4SSsVPxkSvaJQJ5rqlDphWB2TqYKc61AYkrG7B+qOkJZ3FabxVaY/GIg2y1bwCN6R+e30gCYWQ0cz5TCRqLqvGz/AsxkESVtkVj2xQHOBN+cKSaEJ3NCsYanfag+5HZLYgFOfCA=="
-}</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3224,9 +3212,11 @@
         <is>
           <t>{
   "success": true,
-  "message": "요청 성공",
-  "data": {},
-  "timestamp": "2026-01-30T10:00:00+09:00"
+  "message": "CampaignGroup 목록",
+  "data": [
+    null
+  ],
+  "timestamp": "2026-03-04T09:00:00+09:00"
 }</t>
         </is>
       </c>
@@ -3237,13 +3227,7 @@
           <t>Response Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "G95WBgtt2l8EkUe4SSsVPxkSvaJQJ5rqlDphWB2TqYKc61AYkrG7B+qOkJZ3FabxVaY/GIg2y1bwCN6R+e30gCYWQ0cz5TCRqLqvGz/AsxkESVtkVj2xQHOBN+cKSaEJ3NCsYanfag+5HZLYgFOfCA=="
-}</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3402,13 +3386,7 @@
           <t>Request Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "+0gvit7igCOB2BwzFRDFGErB0Ec+z235iOaLmBreSuMY97dKGJWwyYSHXxH/1XY/1f1G//qiedHBmbQEk9123fHm+fcvVaiONRRWEh7tWof0U7n+tEleoRDCgNgxOSGU9LvHamKbl+qnAS7esPNME0tJNJnfizGbbiT8iS5VgnL+7rdPed9bDzor6an5fAP7w7GuA/dr4mtEud6jiBkNAXckm3dC9+HK3k+TN3ncTUV5R7aBldbRG6EoUvtLCp+NRw91SeEq8HoNU7R/e9xEbu88wwnrb3rSewH5TOwBv3Ao/8n1EyFou1Ck9inxIrwXW/hMuRdcuCUhWuVSDa6vEVhThNu0x91vdMV1DaRPAYFUgknzsRmg2T0Dif0hy3TFBZqUcf2d+UdDv9cp4cgIPq7mIQ0K5x4HE6jL89R0PgfEbhtxIBGtnzwfdtwKvhwLU7wTwzM2uvtgvOapx6s4lreT8dZ/XdZH5t70ri3+026/kJF/CpHqad00SYP0zjGbY7ZnG4pSc0zZg+izlddIl3sVlXljQxH09xUCozWzNdrZ/I2Sc/t6TwP8ZRwZFcdPvxnaRMvdCUVeMvQx6ml2Yk9hRIMqQWiEOCC1tuELEMLXo0uPGTbI+xkeFTLJVTWDC52cr342kIqm3E03J5foxQ=="
-}</t>
-        </is>
-      </c>
+      <c r="B10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -3433,13 +3411,7 @@
           <t>Response Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "G95WBgtt2l8EkUe4SSsVPxkSvaJQJ5rqlDphWB2TqYKc61AYkrG7B+qOkJZ3FabxVaY/GIg2y1bwCN6R+e30gCYWQ0cz5TCRqLqvGz/AsxkESVtkVj2xQHOBN+cKSaEJ3NCsYanfag+5HZLYgFOfCA=="
-}</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3629,13 +3601,7 @@
           <t>Response Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "G95WBgtt2l8EkUe4SSsVP/s7x+txMyb0QeEAVwWz9zcBt5mz2JWOfWIm+hddcVhFvtcAa68WHgN9qihCeawLEN71gGMjQT/irU3bO+RnI8FU51eVEnitujxtB+TYf9tQY6O/wEbvi85dDW2KbNxbQJiNxHnjM0cI8FSysxc42HmF2ru2oFIZKEiUqW9DG/JZpEKJ+pP3s4QkeJOY5kH1PBE5Q1qoo6o4ks+brP+aaLhnRe+/eaE4FcVZUcf4X4JNuloAY2vQXbYL2ezirhWFtbV/p+I6ksE0az/U/RY96qYX7ONL9lt9uDtsAeY3Xhq5Yr8+gA1XVO82i127AXlDqOllSw6FMUlFlGUCIKJdg/2RJRZcSybAIMeq1YB55D13WNH9HO86dRYJXKUOYeRb77TP1sBKv8YX3N0qKiBx7B2CMY7oiM59AxhAPD2as8fHtGGbj98X6JceMgH6dk4LhhLjbt2FIVNASxNUWwIpbQXZFRUP3YG/bHePjGoLuhyfsksD7GEO/dacrDRfryYxJqiBIsuE4Ng4nCSrBS1QVldr/ts42AsJ++HnheTwLNElb17RaOLC44SxMNj8V1G4YUvuqwWLgMGHoIQwpBvBLDG0rxeXDD3/AKIh6PONp4YMCUzuUSHFyGcpwazrQYCe/V7qPozEFmIWAmVvOs9eED8sTHfbT+Hnu3zdd/lyFhCsynEAoe/DUKecNAG186M/+H8oEJobFzRB3r/Lj0LCZ2GklmBjQTbdf+d5lUm3iXWrrVh+RTE2TAdm/k8jrzhh4Kyi+7pGvoZxH1MOalCVaXXK5PMLW4GVWK88sxevJn/SPJUJN8AewpqNJh+pgRKBECIsorSvaUKwOGguHtPElyoqzJZfx3mVz4JpHRiD2UAKA9yOQdjBAR4p4nuDnlQQK7U5FkcPrjUrkBVNbQ//PuTb8PhRBF+xucGSlifJRwQsOaYY/oe0JfohW51KkGEnEYgT4e0kiLXi2KWB5b39Tes="
-}</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3790,13 +3756,7 @@
           <t>Response Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "G95WBgtt2l8EkUe4SSsVPxkSvaJQJ5rqlDphWB2TqYKc61AYkrG7B+qOkJZ3FabxVaY/GIg2y1bwCN6R+e30gCYWQ0cz5TCRqLqvGz/AsxkESVtkVj2xQHOBN+cKSaEJ3NCsYanfag+5HZLYgFOfCA=="
-}</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3986,13 +3946,7 @@
           <t>Response Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "G95WBgtt2l8EkUe4SSsVP/s7x+txMyb0QeEAVwWz9zcBt5mz2JWOfWIm+hddcVhFvtcAa68WHgN9qihCeawLEN71gGMjQT/irU3bO+RnI8FU51eVEnitujxtB+TYf9tQY6O/wEbvi85dDW2KbNxbQJiNxHnjM0cI8FSysxc42HmF2ru2oFIZKEiUqW9DG/JZpEKJ+pP3s4QkeJOY5kH1PBE5Q1qoo6o4ks+brP+aaLhnRe+/eaE4FcVZUcf4X4JNuloAY2vQXbYL2ezirhWFtbV/p+I6ksE0az/U/RY96qYX7ONL9lt9uDtsAeY3Xhq5Yr8+gA1XVO82i127AXlDqOllSw6FMUlFlGUCIKJdg/2RJRZcSybAIMeq1YB55D13WNH9HO86dRYJXKUOYeRb77TP1sBKv8YX3N0qKiBx7B2CMY7oiM59AxhAPD2as8fHtGGbj98X6JceMgH6dk4LhhLjbt2FIVNASxNUWwIpbQXZFRUP3YG/bHePjGoLuhyfsksD7GEO/dacrDRfryYxJqiBIsuE4Ng4nCSrBS1QVldr/ts42AsJ++HnheTwLNElb17RaOLC44SxMNj8V1G4YUvuqwWLgMGHoIQwpBvBLDG0rxeXDD3/AKIh6PONp4YMCUzuUSHFyGcpwazrQYCe/V7qPozEFmIWAmVvOs9eED8sTHfbT+Hnu3zdd/lyFhCsynEAoe/DUKecNAG186M/+H8oEJobFzRB3r/Lj0LCZ2GklmBjQTbdf+d5lUm3iXWrrVh+RTE2TAdm/k8jrzhh4Kyi+7pGvoZxH1MOalCVaXXK5PMLW4GVWK88sxevJn/SPJUJN8AewpqNJh+pgRKBECIsorSvaUKwOGguHtPElyoqzJZfx3mVz4JpHRiD2UAKA9yOQdjBAR4p4nuDnlQQK7U5FkcPrjUrkBVNbQ//PuTb8PhRBF+xucGSlifJRwQsOaYY/oe0JfohW51KkGEnEYgT4e0kiLXi2KWB5b39Tes="
-}</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4151,13 +4105,7 @@
           <t>Request Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "+0gvit7igCOB2BwzFRDFGErB0Ec+z235iOaLmBreSuMY97dKGJWwyYSHXxH/1XY/1f1G//qiedHBmbQEk9123fHm+fcvVaiONRRWEh7tWof0U7n+tEleoRDCgNgxOSGU9LvHamKbl+qnAS7esPNME0tJNJnfizGbbiT8iS5VgnL+7rdPed9bDzor6an5fAP7w7GuA/dr4mtEud6jiBkNAXckm3dC9+HK3k+TN3ncTUV5R7aBldbRG6EoUvtLCp+NRw91SeEq8HoNU7R/e9xEbu88wwnrb3rSewH5TOwBv3Ao/8n1EyFou1Ck9inxIrwXW/hMuRdcuCUhWuVSDa6vEVhThNu0x91vdMV1DaRPAYFUgknzsRmg2T0Dif0hy3TFBZqUcf2d+UdDv9cp4cgIPq7mIQ0K5x4HE6jL89R0PgfEbhtxIBGtnzwfdtwKvhwLU7wTwzM2uvtgvOapx6s4lreT8dZ/XdZH5t70ri3+026/kJF/CpHqad00SYP0zjGbY7ZnG4pSc0zZg+izlddIl3sVlXljQxH09xUCozWzNdrZ/I2Sc/t6TwP8ZRwZFcdPvxnaRMvdCUVeMvQx6ml2Yk9hRIMqQWiEOCC1tuELEMLXo0uPGTbI+xkeFTLJVTWDC52cr342kIqm3E03J5foxQ=="
-}</t>
-        </is>
-      </c>
+      <c r="B10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -4182,13 +4130,7 @@
           <t>Response Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "G95WBgtt2l8EkUe4SSsVPxkSvaJQJ5rqlDphWB2TqYKc61AYkrG7B+qOkJZ3FabxVaY/GIg2y1bwCN6R+e30gCYWQ0cz5TCRqLqvGz/AsxkESVtkVj2xQHOBN+cKSaEJ3NCsYanfag+5HZLYgFOfCA=="
-}</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4330,9 +4272,11 @@
         <is>
           <t>{
   "success": true,
-  "message": "요청 성공",
-  "data": {},
-  "timestamp": "2026-01-30T10:00:00+09:00"
+  "message": "캠페인 목록",
+  "data": [
+    null
+  ],
+  "timestamp": "2026-03-04T09:00:00+09:00"
 }</t>
         </is>
       </c>
@@ -4343,13 +4287,7 @@
           <t>Response Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "G95WBgtt2l8EkUe4SSsVPxkSvaJQJ5rqlDphWB2TqYKc61AYkrG7B+qOkJZ3FabxVaY/GIg2y1bwCN6R+e30gCYWQ0cz5TCRqLqvGz/AsxkESVtkVj2xQHOBN+cKSaEJ3NCsYanfag+5HZLYgFOfCA=="
-}</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4493,13 +4431,7 @@
           <t>Request Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "+0gvit7igCOB2BwzFRDFGEgBDuOsN8yulVB9+ENwWN0CZSRA0RBW/c9pel6wOHxPyW6mMaMpCU+fD+3TmsOA0KZC+Z6pVBToKqL6IdxL+XFmTe17i7HYBk0yn9eUduh7gSP/PpBLD2mSNaRHOsIm62fz7sJPfO3ZLUEnzHDA4pHkVh7WlRY93a4EMnVLJKW1xNQs7Dabx8fN3/eXgsx7kA=="
-}</t>
-        </is>
-      </c>
+      <c r="B10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -4524,13 +4456,7 @@
           <t>Response Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "G95WBgtt2l8EkUe4SSsVPxkSvaJQJ5rqlDphWB2TqYKc61AYkrG7B+qOkJZ3FabxVaY/GIg2y1bwCN6R+e30gCYWQ0cz5TCRqLqvGz/AsxkESVtkVj2xQHOBN+cKSaEJ3NCsYanfag+5HZLYgFOfCA=="
-}</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4685,13 +4611,7 @@
           <t>Response Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "G95WBgtt2l8EkUe4SSsVPxkSvaJQJ5rqlDphWB2TqYKc61AYkrG7B+qOkJZ3FabxVaY/GIg2y1bwCN6R+e30gCYWQ0cz5TCRqLqvGz/AsxkESVtkVj2xQHOBN+cKSaEJ3NCsYanfag+5HZLYgFOfCA=="
-}</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4813,7 +4733,14 @@
           <t>Request Example (Plain)</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>{
+  "username": "appadm",
+  "password": "secret"
+}</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -4829,7 +4756,22 @@
           <t>Response Example (Plain)</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>{
+  "success": true,
+  "message": "토큰 발급",
+  "data": {
+    "tokenType": "Bearer",
+    "accessToken": "eyJhbGciOiJIUzI1NiJ9...",
+    "refreshToken": "eyJhbGciOiJIUzI1NiJ9...",
+    "accessTokenExpiresIn": 900,
+    "refreshTokenExpiresIn": 604800
+  },
+  "timestamp": "2026-03-04T09:00:00+09:00"
+}</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -4992,13 +4934,7 @@
           <t>Response Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "G95WBgtt2l8EkUe4SSsVPxkSvaJQJ5rqlDphWB2TqYKc61AYkrG7B+qOkJZ3FabxVaY/GIg2y1bwCN6R+e30gCYWQ0cz5TCRqLqvGz/AsxkESVtkVj2xQHOBN+cKSaEJ3NCsYanfag+5HZLYgFOfCA=="
-}</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5222,13 +5158,7 @@
           <t>Response Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "G95WBgtt2l8EkUe4SSsVP+LTt5lXuLcukPGAVht8uCLvDHSlzDWuFRa3dXnrBNkCRxy90VXiXAk9l/WQ2QQBiteEJYWIhXXnA3egKROVqZed+xRum5I0Ol3onudRTfO8CiCp2el4DGrQI99Qh6g10q3RzsqpYPoN4eExLxejXpBGybo1h0TiAVcbtM/M//GqqQPFjky5ea9nYBJTNr7HdSpwZlOGr2ijq0Ehgyek/XJQptc7/iIHni2GF29jF4uOKpCNNpVq2wT+EBrrtREdxiR9EfyRKrvD/4JO58ahF+j35j1GeEESDYzysnNjS61B4G0WM0+3Hhsox+PL0x8PsbywsgBiMkcEFMxN9AbzDBeYRhZKhDkobhjQ5GTyn5upHWv1JyDEnyu00UyOH/m93fX4TFIW9tTIhA+MRxI/6xmUHU7Lr1I4XQVuCZ5mxALx4aIsOzYmEB7lrVDEsTR76gXWAlCHhdN8Ek0ZDG1mfw8lPWDruq7ZAHpjjyfJhO9P7YU27Ei9ULGtwevCM0RwupJ5sFVn22s/z/j/KtkxMVKMHVVq0y2sm0ND9Mc8HTerXN1g3wzekUqX4yzpI/XbwwnjuuLMJyfJo4+DlVCRxXZHFAjfCFMcLX5IHSr9+uoOtV5Q6oIPfnUWjtDoL32r+dfDKfhNdW1S2kLTr8qde0Y5/ye1+odM8330LTZFvTE/8/j7ys6oGNNINKzx7zPNHRH6SaTVQ36vqSbg5RVmF4zgQnZ/m+phS2hFbUA4PJrf8VLxDRfySx8b+O+4rTmwNAT3V+Wd+Fo8r8VIUMVEutxic6ylLenzEuLXLpLIObGSeERHyzty71eXNFepWK2bnZdWiAZFWzdQVCaH3NrHDdxc+u8npdxpWRW017Gkf7yPnBLC2S6+uVpl4PHNixD0pSDSSaRMfxKZ6p3TvJWrWg0Gb6sLef38uBGx83QyDjb2t0LK9eMDzuqOpCvaf8VURxVUtV2DZ+7nelDHncpYgdTA/uJzG88h2ybhN0vgA7wRmVMvsG6zaapreHSsZvaTlsS3v0PENml97/O+SmU82mxYplDVvl8wEua8ibAGL01PILcjMub0Dj0jec5z/8RSC4nzJ4JPyzEjMG48BYKiJnjLu5cWSpk9Fa3qeKRu56iXxoLDzXSPrdqTEneWEYzrXKM+bXHsbo1JZ16QzYLHlQpp3eLPr5DoUB/+dMwbgG+wjrZvxkSIWfzIh1Aj6yExJ58g16xPHYIQz6qUZ7Wm/yKqZycGaIll3M1Rik3nd3ASgP2/G0PhmBpnExWxHP3gCFYMEROQE+AAbWsXci4+CzklZy1agV52cZJtbxURq77bbrhafjI6axvdegPlrEE2jZJCUb9lJYoEayngV/3KdsGQvt4pWwi8schcVWuDzL5znIju+F+b7/WKropMS63PSJFqmlE/5qu66IDI/JIZy0wcCLSAGmHKCwwKLGvBx52j9dsf8eo7Ftc71OzDwlxurL+/TL2yrg3ZlnsTfIXXtc2So0K5eheMoYVYIyDGwAMm3qB47BL953jKjB1XiFPNlOl1XhI1XikEHy8ItcrYnsKS/EMKsHZY6pzdSm2sYYM7I7hWUigd12dBxJkT4SKJ2bAAPa8IM9zgbSDU0JgvaYgBscJBzpvdutsVA1b+S4Bj"
-}</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5372,13 +5302,7 @@
           <t>Request Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "+0gvit7igCOB2BwzFRDFGEgBDuOsN8yulVB9+ENwWN0CZSRA0RBW/c9pel6wOHxPyW6mMaMpCU+fD+3TmsOA0KZC+Z6pVBToKqL6IdxL+XFmTe17i7HYBk0yn9eUduh7gSP/PpBLD2mSNaRHOsIm62fz7sJPfO3ZLUEnzHDA4pHkVh7WlRY93a4EMnVLJKW1xNQs7Dabx8fN3/eXgsx7kA=="
-}</t>
-        </is>
-      </c>
+      <c r="B10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -5472,13 +5396,7 @@
           <t>Response Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "G95WBgtt2l8EkUe4SSsVP+LTt5lXuLcukPGAVht8uCJnDYIMzGrnp5O5HAwF9eyheQf8GZrXr1AC6t+IxjI6YcmQ2zxJ55B87ea9jeESLmgq8JY0cLNVYR7WBqDQFDjg9/FiLvcPbCpQH3YkPhfpKs5V+ivKFRNPOXA4lwTSEsHIQ8BS12i0TwZwsdtbNdKSGdXLVsjOHFOzRmmK/PVVtzLurl0MNU5iPuKb0nn932GzpzG/EHRRweis+R7JGHaguTtInNVNYXqBpLrJlhQMnyyC4H7Itl1yny9wyu5XRzG+xXLrbMIvFGxrVS4dNgp+VbITS6zcvfbGMvrv1OWLAEC7PT05RPvjxHYDazb8vsfjMbIxKNrlAmayAr9wKac7AU92r+jZC9huppJ/elKnWECKFq6BYVU1rWkpCJaVsJVDaowSKwElggsAzzlPAmYJEYkNIWaVHwVo/R8w+CFpIRNrOevKsGs0+kmIelFaMFe7vIgvwl235OS+OuF/WWNEjRNecorO/GLfrdQ+EOe6R/TYxyK5yV7YGTzYgZyyHJIb42IAEf/wmeMU3o2YCZFd7XtGOHeGSLR38WioZlTpXv6wlqWc5P13a+FyIhD/uVacc0614n9mBV17Zhvi83l2Dbktebu6rK14QSFOKJ3EX92kItKgCOlc7ZJsNr26wzJv64nd5jJtVqgfheEAb1maOyG1Wuc7IOObMLqGQF6Q+q8E00wBdsTpTpf5+pZpgF71MZ3Rm7Zo6lrzFknLjWty7Q6L+H9PUawW5YLEvVn2ItV48WHGRpcAaKcOqeDSrHv6EGeIQzgyAIcQ+rU4dxurYpJVO071kIcKdLtLe9noy16DYkAH9gOoZyFLltpGYvIlzCKOFOt913TfQUE+0nZ2L9/mORC2ii5KvGoleE5weaaEAtgKMRx4LRIv1C2FeEjeaZHb4DoGY3W5LFFWtyVNpcAcT6wjvo9HFctkMG9FoYK+QJnYb+60evUgj/oLYwgNyRSy2sfyA0CkEknE8aKVl68iYGAP0ICBRIoVfhx5whG2hMrmdSiglAv4iAbM4IXA+UV6QMk/IpDALbvt8CCCsX5xIsdGetMr4jNHGD+HI+ZhphvKxDKGOXMqONLwAbkr83ljkzMoHvk27ChS7X/2RbciJGxXXu/VbiwYRYr4GT+UqKezzlrJGJ1j0Yoa9cHznn9aPCAGQE00iz95yn7dmBGEdGctLD9I0Yt+uK3h+qYZ+YIDkxIi86ad/aSXzHDHuBYHPPUKnNSqSXtrPzXobKtzlXJQz0uaP9Rf/xh6HFxx5qMGAhGiHIIJSC8/EbKy/5ak3Bm03YzEYdB0agrWjijnyuwKKzu3Q9JJ+Hx3aeoyuSilJygY6cMdv4UYhtkZ509eKFK17YJCfw+SqS6op0ZfpdGs4Puk+E34Z0x1RAoTm2xo6JiQ+E/gkWotBfciXEAOV+qR8sg2Ji5g+BLs89RHgBoVLzzmlrHWcLuECUZHn1jvA9h1VEoschD5mBe66NfHovaogqOpI2oC+QW2FEM1F8h5GgSLIZYIFtJqeal5NnzntipkHHkq01cF2p1McE0X7jVIsTVkhg48wnGL0p0BLC5oyM0lU1EWfrliQX+3ktPwsYi2EPxzGWqj9hg7nUNUkQUMJbIZHV1z1hZv"
-}</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5620,9 +5538,11 @@
         <is>
           <t>{
   "success": true,
-  "message": "요청 성공",
-  "data": {},
-  "timestamp": "2026-01-30T10:00:00+09:00"
+  "message": "Filter 목록",
+  "data": [
+    null
+  ],
+  "timestamp": "2026-03-04T09:00:00+09:00"
 }</t>
         </is>
       </c>
@@ -5633,13 +5553,7 @@
           <t>Response Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "G95WBgtt2l8EkUe4SSsVPxkSvaJQJ5rqlDphWB2TqYKc61AYkrG7B+qOkJZ3FabxVaY/GIg2y1bwCN6R+e30gCYWQ0cz5TCRqLqvGz/AsxkESVtkVj2xQHOBN+cKSaEJ3NCsYanfag+5HZLYgFOfCA=="
-}</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5785,13 +5699,7 @@
           <t>Request Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "+0gvit7igCOB2BwzFRDFGPQhD3UEa/g1rYC/fpzq6G3WHoBmO353Yx8smyQtlrPwi2oUmWg3SWeZsopLBz0cu6mMaVCiynIcdVUFpKTL2oeLjW5Dr1iS/+X+rEJos8I/eRk05GQfHEa4Yhu3A421+ODFuCn29T+FFHTap2K1/92lG+a8yO6dASGXHQr5kEQ1ef45qQp7kdrlVQE+qPjow3HXx5C8+ldknRn4HdxgJtWFZGH+hFW81Wb0OE9xgYJbOlfb7bZMzbbWDISFiAf80DZzTjFqs/GT7e1Uja1dZWs="
-}</t>
-        </is>
-      </c>
+      <c r="B10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -5816,13 +5724,7 @@
           <t>Response Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "G95WBgtt2l8EkUe4SSsVPxkSvaJQJ5rqlDphWB2TqYKc61AYkrG7B+qOkJZ3FabxVaY/GIg2y1bwCN6R+e30gCYWQ0cz5TCRqLqvGz/AsxkESVtkVj2xQHOBN+cKSaEJ3NCsYanfag+5HZLYgFOfCA=="
-}</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5990,13 +5892,7 @@
           <t>Response Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "G95WBgtt2l8EkUe4SSsVP9ze8keYVzlEeBQL4DINWcPPyTPG6b3IXsOoASA3PtFFqUFPtWc9qQtR+jOvYxCF75e3azEZDGSXQieAgBez1IYvp19d36VY99cPTLasI3WunF+8SwOubZW+I95rsooF38HicWcc3MPNgZyUGiinjM/jWdWyel36KjdNCFhQ3xqXx3jh8kHQkIX6Aza+7x8Wy55DYwlQ6l1xGvup2rbLhZXMy6ChgWu0lzbdthD7bFNoEiy6/2bCgUV8SwH5GGIPUtE19Z24MYQpk4COpmii8H2V5MItOYzP38m030kLtraScIwFnhgKrM/YUBeDf56PLA1eSkQQyZ7OwI+YjdSvJyIBxCCitZv2jDUMNwzj2s3s60QnrXK5wIJiVCHrZ2ukQz+fpp+LrsZkqoLQ3BlhnmmLYF5nVezJyr68O01XBE6m+V/n3goy6JLXH0l62Hb5PA=="
-}</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6151,13 +6047,7 @@
           <t>Response Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "G95WBgtt2l8EkUe4SSsVPxkSvaJQJ5rqlDphWB2TqYKc61AYkrG7B+qOkJZ3FabxVaY/GIg2y1bwCN6R+e30gCYWQ0cz5TCRqLqvGz/AsxkESVtkVj2xQHOBN+cKSaEJ3NCsYanfag+5HZLYgFOfCA=="
-}</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6325,13 +6215,7 @@
           <t>Response Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "G95WBgtt2l8EkUe4SSsVP9ze8keYVzlEeBQL4DINWcPPyTPG6b3IXsOoASA3PtFFqUFPtWc9qQtR+jOvYxCF75e3azEZDGSXQieAgBez1IYvp19d36VY99cPTLasI3WunF+8SwOubZW+I95rsooF38HicWcc3MPNgZyUGiinjM/jWdWyel36KjdNCFhQ3xqXx3jh8kHQkIX6Aza+7x8Wy55DYwlQ6l1xGvup2rbLhZXMy6ChgWu0lzbdthD7bFNoEiy6/2bCgUV8SwH5GGIPUtE19Z24MYQpk4COpmii8H2V5MItOYzP38m030kLtraScIwFnhgKrM/YUBeDf56PLA1eSkQQyZ7OwI+YjdSvJyIBxCCitZv2jDUMNwzj2s3s60QnrXK5wIJiVCHrZ2ukQz+fpp+LrsZkqoLQ3BlhnmmLYF5nVezJyr68O01XBE6m+V/n3goy6JLXH0l62Hb5PA=="
-}</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6477,13 +6361,7 @@
           <t>Request Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "+0gvit7igCOB2BwzFRDFGPQhD3UEa/g1rYC/fpzq6G3WHoBmO353Yx8smyQtlrPwi2oUmWg3SWeZsopLBz0cu6mMaVCiynIcdVUFpKTL2ofPxKaMcVMyTKPOSqQYC/PQ8Qb60Jcf6KL7laiQOT116efqsPYJ+q5RvhrFtqZ7Ea9WpodONISXvdTHisH9SiVG5AHQNgLXcm7w2aixx92lAHKlVqwwY2xdRMBujuITMUgCg8otnkqZd+AkdaqR6xgEM5764/J6Rt66YFpP8HGqzZ82/tkbCKOgFBmPswCZbbjB/Vevt+C6U9OXP8QhxNN1"
-}</t>
-        </is>
-      </c>
+      <c r="B10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -6508,13 +6386,7 @@
           <t>Response Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "G95WBgtt2l8EkUe4SSsVPxkSvaJQJ5rqlDphWB2TqYKc61AYkrG7B+qOkJZ3FabxVaY/GIg2y1bwCN6R+e30gCYWQ0cz5TCRqLqvGz/AsxkESVtkVj2xQHOBN+cKSaEJ3NCsYanfag+5HZLYgFOfCA=="
-}</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6656,9 +6528,11 @@
         <is>
           <t>{
   "success": true,
-  "message": "요청 성공",
-  "data": {},
-  "timestamp": "2026-01-30T10:00:00+09:00"
+  "message": "Format 목록",
+  "data": [
+    null
+  ],
+  "timestamp": "2026-03-04T09:00:00+09:00"
 }</t>
         </is>
       </c>
@@ -6669,13 +6543,7 @@
           <t>Response Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "G95WBgtt2l8EkUe4SSsVPxkSvaJQJ5rqlDphWB2TqYKc61AYkrG7B+qOkJZ3FabxVaY/GIg2y1bwCN6R+e30gCYWQ0cz5TCRqLqvGz/AsxkESVtkVj2xQHOBN+cKSaEJ3NCsYanfag+5HZLYgFOfCA=="
-}</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6797,7 +6665,13 @@
           <t>Request Example (Plain)</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>{
+  "refreshToken": "eyJhbGciOiJIUzI1NiJ9..."
+}</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -6813,7 +6687,22 @@
           <t>Response Example (Plain)</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>{
+  "success": true,
+  "message": "토큰 갱신",
+  "data": {
+    "tokenType": "Bearer",
+    "accessToken": "eyJhbGciOiJIUzI1NiJ9...",
+    "refreshToken": "eyJhbGciOiJIUzI1NiJ9...",
+    "accessTokenExpiresIn": 900,
+    "refreshTokenExpiresIn": 604800
+  },
+  "timestamp": "2026-03-04T09:00:00+09:00"
+}</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -6976,13 +6865,7 @@
           <t>Response Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "G95WBgtt2l8EkUe4SSsVPxkSvaJQJ5rqlDphWB2TqYKc61AYkrG7B+qOkJZ3FabxVaY/GIg2y1bwCN6R+e30gCYWQ0cz5TCRqLqvGz/AsxkESVtkVj2xQHOBN+cKSaEJ3NCsYanfag+5HZLYgFOfCA=="
-}</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7137,13 +7020,7 @@
           <t>Response Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "G95WBgtt2l8EkUe4SSsVPxkSvaJQJ5rqlDphWB2TqYKc61AYkrG7B+qOkJZ3FabxVaY/GIg2y1bwCN6R+e30gCYWQ0cz5TCRqLqvGz/AsxkESVtkVj2xQHOBN+cKSaEJ3NCsYanfag+5HZLYgFOfCA=="
-}</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7285,9 +7162,11 @@
         <is>
           <t>{
   "success": true,
-  "message": "요청 성공",
-  "data": {},
-  "timestamp": "2026-01-30T10:00:00+09:00"
+  "message": "TableAccess 목록",
+  "data": [
+    null
+  ],
+  "timestamp": "2026-03-04T09:00:00+09:00"
 }</t>
         </is>
       </c>
@@ -7298,13 +7177,7 @@
           <t>Response Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "G95WBgtt2l8EkUe4SSsVPxkSvaJQJ5rqlDphWB2TqYKc61AYkrG7B+qOkJZ3FabxVaY/GIg2y1bwCN6R+e30gCYWQ0cz5TCRqLqvGz/AsxkESVtkVj2xQHOBN+cKSaEJ3NCsYanfag+5HZLYgFOfCA=="
-}</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7459,13 +7332,7 @@
           <t>Response Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "G95WBgtt2l8EkUe4SSsVPxkSvaJQJ5rqlDphWB2TqYKc61AYkrG7B+qOkJZ3FabxVaY/GIg2y1bwCN6R+e30gCYWQ0cz5TCRqLqvGz/AsxkESVtkVj2xQHOBN+cKSaEJ3NCsYanfag+5HZLYgFOfCA=="
-}</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7620,13 +7487,7 @@
           <t>Response Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "G95WBgtt2l8EkUe4SSsVPxkSvaJQJ5rqlDphWB2TqYKc61AYkrG7B+qOkJZ3FabxVaY/GIg2y1bwCN6R+e30gCYWQ0cz5TCRqLqvGz/AsxkESVtkVj2xQHOBN+cKSaEJ3NCsYanfag+5HZLYgFOfCA=="
-}</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7768,9 +7629,11 @@
         <is>
           <t>{
   "success": true,
-  "message": "요청 성공",
-  "data": {},
-  "timestamp": "2026-01-30T10:00:00+09:00"
+  "message": "treatment 목록",
+  "data": [
+    null
+  ],
+  "timestamp": "2026-03-04T09:00:00+09:00"
 }</t>
         </is>
       </c>
@@ -7781,13 +7644,7 @@
           <t>Response Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "G95WBgtt2l8EkUe4SSsVPxkSvaJQJ5rqlDphWB2TqYKc61AYkrG7B+qOkJZ3FabxVaY/GIg2y1bwCN6R+e30gCYWQ0cz5TCRqLqvGz/AsxkESVtkVj2xQHOBN+cKSaEJ3NCsYanfag+5HZLYgFOfCA=="
-}</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7942,13 +7799,7 @@
           <t>Response Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "G95WBgtt2l8EkUe4SSsVPxkSvaJQJ5rqlDphWB2TqYKc61AYkrG7B+qOkJZ3FabxVaY/GIg2y1bwCN6R+e30gCYWQ0cz5TCRqLqvGz/AsxkESVtkVj2xQHOBN+cKSaEJ3NCsYanfag+5HZLYgFOfCA=="
-}</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8103,13 +7954,7 @@
           <t>Response Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "G95WBgtt2l8EkUe4SSsVPxkSvaJQJ5rqlDphWB2TqYKc61AYkrG7B+qOkJZ3FabxVaY/GIg2y1bwCN6R+e30gCYWQ0cz5TCRqLqvGz/AsxkESVtkVj2xQHOBN+cKSaEJ3NCsYanfag+5HZLYgFOfCA=="
-}</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8412,7 +8257,13 @@
           <t>Request Example (Plain)</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>{
+  "encData": "string"
+}</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -8659,13 +8510,7 @@
           <t>Request Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "Y2ExYNZ3kxZbU1BdO5rF9UJ2WHO5wvKl1WwQ8zzZnxeiLKS8oiRJyGIgV1Y9TX3YfUCJQb6FzfmfYVVtOzxsSXxVJwxvwoV9cLIPIdaSrApfaFB3sF67eE+AlfgmRyHe0Elu96NK4u3TMWao1ibFoHuvhG3MHBGlHdAWmgwQ5tM6tTYhT1KG/LWRWIcLD8kW0sfwtMQ09QNvWCQfrXXtdACe9OLI5XgJ/GAg2hnkdC7I7ncgHM+HUvT8a+sxfX2hPzJYFuhlOToMfkJFmprsVTKj2ZP3A9SMqFq59w87moAuMG+QdNVTeGBEdwlFqPntIt6M6yJ62DkFaK+RxETuvPUymC5uN/wzASBygSwUokEl7tNaCpp0hTdgqV46uEYKUFRQmWMje5gK5R6RkIFt827YGdTQGKVjTWAgtnTVFkRr1CzNGpq4gv2s7jdTq5jmDZ+a1frEsvbwXA1m/cYKeQSn0cZ+rqgzboELvpvHL4hvH+Xf/TH3BmqCr1qAm4l9srjekljJm6d1Iuui3kTlrP8UxGhAv+piT2l/Ovxbv3G+sFpMWMDd8FVJnkaInaftvS9Llzt0uOMaYSlU7z87vwr1SsB4IMK1MQKQWi5gQ8CbwhGJlwcu/VCD5uFKy+FEGsNuVFHQsypsXh9X4O3JvwMuJN2ErjXYsSc4KXvXj/hSg34848HHYTx3RxbVGGFcz6bkS7M+a6YqA64uc/X/dZ2GEmfLvbtX2kyYniPcy07Vxso9y0baOO3DYXrMz1cy7hTZiv8z5y8Ans/Ts215ZnRQM7AtsxWCFy89epxSZnJLrtdA3PFEMvKYueeyKVUTxtijfcnD20Sc+d0vZJQSrTHJFp4iMRnjsAbxnwzVHl3qCBAOSLSFhfBMgw5HnXLp2zJSM1Z9gUfF7rs2H9Wyh2deYmMR5z2ulyb8cez4TS9kZ81tFdyTruOzt0J7jNd4wnP7l3Ii6qynNSFkLjlgwkwuY8H+/dBxytIE9liMyxVIzZWwPSA8fu3SGH5vsq/Vo107iGja0SX4OPECurEnX2DP00VdWCggIKC60AeF90PySh5RRUdHI8eLvZeL5+Hh13KFhJjuR88N+315ZkVyuSkOE7pYTxEYGm1QQc9J1RXK6hQqzLiAVrZVe4xUvmSCGAvJrPMN18LYAsu+pqTrHl+rJihIPpkQZwvWdHwQHHNue+oUGjg6dlmrQ4S3KU+xCPHIbtfm+GSG1Pme3/dE6wornSo2xeO+2QOqTJ38TFKoyc2+V6mQnI/lPrGkhT+RcrugF09Ji4+phRQr8KMTXVhT4l8UNVt4UZMvieEn96FAYZylxscYb+kJ9X1qT2FVp80uoruqsa47LpeoHCF02CXn5QDZTTLMTFNBTEh+vbFWiezJws42Y23Q42m+kATaTjcwD8NQSnbwDTiCzctWM8b3aQ5pGIVFKGG2sRm6TKfnGa+U8CbKcjDH+f1FBBbQq3fUBkIjlhUQ+6NDwd5GmL02aiQ527snP6mqdWRr49+Rc0JVTk+JbclEe3prw173fwqtsY67AadSlfsrWU2GOZ7hbcDNjnB2nMZVH5Nq6LP5rm57reGdgI9CDDdz8wc0NTRDTn7Dp80Z3kGy755ML2oNVULCt9Tj+I7ef9G/hKucSBLm/KTK6eB6Xer1km3LLVIEv/dJeFzWfYDyg8/YfA=="
-}</t>
-        </is>
-      </c>
+      <c r="B10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -8690,13 +8535,7 @@
           <t>Response Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "G95WBgtt2l8EkUe4SSsVPxkSvaJQJ5rqlDphWB2TqYKc61AYkrG7B+qOkJZ3FabxVaY/GIg2y1bwCN6R+e30gCYWQ0cz5TCRqLqvGz/AsxkESVtkVj2xQHOBN+cKSaEJ3NCsYanfag+5HZLYgFOfCA=="
-}</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8818,7 +8657,13 @@
           <t>Request Example (Plain)</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>{
+  "key": null
+}</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -8996,13 +8841,7 @@
           <t>Request Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "DEdPAqbNv4YS9U1FGOSH62v5L0nZ0+qVlj+Bc2ThYqb/PFo//cYLVgkMnYR60DN8"
-}</t>
-        </is>
-      </c>
+      <c r="B10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -9027,13 +8866,7 @@
           <t>Response Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "G95WBgtt2l8EkUe4SSsVPxkSvaJQJ5rqlDphWB2TqYKc61AYkrG7B+qOkJZ3FabxVaY/GIg2y1bwCN6R+e30gCYWQ0cz5TCRqLqvGz/AsxkESVtkVj2xQHOBN+cKSaEJ3NCsYanfag+5HZLYgFOfCA=="
-}</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9170,13 +9003,7 @@
           <t>Request Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "DEdPAqbNv4YS9U1FGOSH62v5L0nZ0+qVlj+Bc2ThYqb/PFo//cYLVgkMnYR60DN8"
-}</t>
-        </is>
-      </c>
+      <c r="B10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -9201,13 +9028,7 @@
           <t>Response Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "G95WBgtt2l8EkUe4SSsVPxkSvaJQJ5rqlDphWB2TqYKc61AYkrG7B+qOkJZ3FabxVaY/GIg2y1bwCN6R+e30gCYWQ0cz5TCRqLqvGz/AsxkESVtkVj2xQHOBN+cKSaEJ3NCsYanfag+5HZLYgFOfCA=="
-}</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9344,13 +9165,7 @@
           <t>Request Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "DEdPAqbNv4YS9U1FGOSH62v5L0nZ0+qVlj+Bc2ThYqb/PFo//cYLVgkMnYR60DN8"
-}</t>
-        </is>
-      </c>
+      <c r="B10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -9375,13 +9190,7 @@
           <t>Response Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "G95WBgtt2l8EkUe4SSsVPxkSvaJQJ5rqlDphWB2TqYKc61AYkrG7B+qOkJZ3FabxVaY/GIg2y1bwCN6R+e30gCYWQ0cz5TCRqLqvGz/AsxkESVtkVj2xQHOBN+cKSaEJ3NCsYanfag+5HZLYgFOfCA=="
-}</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9518,13 +9327,7 @@
           <t>Request Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "DEdPAqbNv4YS9U1FGOSH62v5L0nZ0+qVlj+Bc2ThYqb/PFo//cYLVgkMnYR60DN8"
-}</t>
-        </is>
-      </c>
+      <c r="B10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -9549,13 +9352,7 @@
           <t>Response Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "G95WBgtt2l8EkUe4SSsVPxkSvaJQJ5rqlDphWB2TqYKc61AYkrG7B+qOkJZ3FabxVaY/GIg2y1bwCN6R+e30gCYWQ0cz5TCRqLqvGz/AsxkESVtkVj2xQHOBN+cKSaEJ3NCsYanfag+5HZLYgFOfCA=="
-}</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9695,13 +9492,7 @@
           <t>Request Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "DEdPAqbNv4YS9U1FGOSH62v5L0nZ0+qVlj+Bc2ThYqa+c0bKnPREtF512ovnFgjPlcUVIJxD9AFZ9hrDQ2V2pEYzMC6BdQEW38hbYDUSzb4WTDmOjC1xXlQCT5DzWhdPugy8bgOnwQMcXghrDUSLkl1YX8j85Np12jj52RA56Lc="
-}</t>
-        </is>
-      </c>
+      <c r="B10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -9726,13 +9517,7 @@
           <t>Response Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "G95WBgtt2l8EkUe4SSsVPxkSvaJQJ5rqlDphWB2TqYKc61AYkrG7B+qOkJZ3FabxVaY/GIg2y1bwCN6R+e30gCYWQ0cz5TCRqLqvGz/AsxkESVtkVj2xQHOBN+cKSaEJ3NCsYanfag+5HZLYgFOfCA=="
-}</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9869,13 +9654,7 @@
           <t>Request Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "DEdPAqbNv4YS9U1FGOSH62v5L0nZ0+qVlj+Bc2ThYqb/PFo//cYLVgkMnYR60DN8"
-}</t>
-        </is>
-      </c>
+      <c r="B10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -9900,13 +9679,7 @@
           <t>Response Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "G95WBgtt2l8EkUe4SSsVPxkSvaJQJ5rqlDphWB2TqYKc61AYkrG7B+qOkJZ3FabxVaY/GIg2y1bwCN6R+e30gCYWQ0cz5TCRqLqvGz/AsxkESVtkVj2xQHOBN+cKSaEJ3NCsYanfag+5HZLYgFOfCA=="
-}</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10061,13 +9834,7 @@
           <t>Response Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "G95WBgtt2l8EkUe4SSsVPxkSvaJQJ5rqlDphWB2TqYKc61AYkrG7B+qOkJZ3FabxVaY/GIg2y1bwCN6R+e30gCYWQ0cz5TCRqLqvGz/AsxkESVtkVj2xQHOBN+cKSaEJ3NCsYanfag+5HZLYgFOfCA=="
-}</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10658,9 +10425,11 @@
         <is>
           <t>{
   "success": true,
-  "message": "요청 성공",
-  "data": {},
-  "timestamp": "2026-01-30T10:00:00+09:00"
+  "message": "콜링리스트 목록",
+  "data": [
+    null
+  ],
+  "timestamp": "2026-03-04T09:00:00+09:00"
 }</t>
         </is>
       </c>
@@ -10671,13 +10440,7 @@
           <t>Response Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "G95WBgtt2l8EkUe4SSsVPxkSvaJQJ5rqlDphWB2TqYKc61AYkrG7B+qOkJZ3FabxVaY/GIg2y1bwCN6R+e30gCYWQ0cz5TCRqLqvGz/AsxkESVtkVj2xQHOBN+cKSaEJ3NCsYanfag+5HZLYgFOfCA=="
-}</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13086,13 +12849,7 @@
           <t>Request Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "+0gvit7igCOB2BwzFRDFGGZ779xO8Ha6BtWSL4XJDeOp/piL2v5rlkvznXX6ld3sEU7LR8Pp6JYOvBYg5dO10QJLWPBNODCLkbEf5B0AHI8RrtgzKtSBfmEjnvKvL3+rTfKj5RDUEIZRIIy0OJRAldMMu5mc3TfEKN9vCIW7WDutx7AIXhL8H9zcPeLZA1WLYCBoQjJS75Btn8yorDfzrI8hYwX7il3dqtkoYCVnGjggkouVt03Up+YaNZ2aIQurkPAelt9kZFtAe1hQZBuEJudSpL3PC9yH1y74T7TgxuwX60PcoyDHNTlIYivze7nwB6QKbYZfrQzwV3mpT/LpL+oo2QsIO4SI0WvdSx3EdRVpZH3GUnvvQoEDued4eAITeLzAJSWsGuY7fWThWUA+mnknmO5MySABRZw2H9vpobib7dzKwZBo/ttM2gIKrKO9"
-}</t>
-        </is>
-      </c>
+      <c r="B10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -13117,13 +12874,7 @@
           <t>Response Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "G95WBgtt2l8EkUe4SSsVPxkSvaJQJ5rqlDphWB2TqYKc61AYkrG7B+qOkJZ3FabxVaY/GIg2y1bwCN6R+e30gCYWQ0cz5TCRqLqvGz/AsxkESVtkVj2xQHOBN+cKSaEJ3NCsYanfag+5HZLYgFOfCA=="
-}</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13572,13 +13323,7 @@
           <t>Response Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "G95WBgtt2l8EkUe4SSsVPxkSvaJQJ5rqlDphWB2TqYKc61AYkrG7B+qOkJZ3FabxVaY/GIg2y1bwCN6R+e30gCYWQ0cz5TCRqLqvGz/AsxkESVtkVj2xQHOBN+cKSaEJ3NCsYanfag+5HZLYgFOfCA=="
-}</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13733,13 +13478,7 @@
           <t>Response Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "G95WBgtt2l8EkUe4SSsVPxkSvaJQJ5rqlDphWB2TqYKc61AYkrG7B+qOkJZ3FabxVaY/GIg2y1bwCN6R+e30gCYWQ0cz5TCRqLqvGz/AsxkESVtkVj2xQHOBN+cKSaEJ3NCsYanfag+5HZLYgFOfCA=="
-}</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13894,13 +13633,7 @@
           <t>Response Example (Encrypted)</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>{
-  "encData": "G95WBgtt2l8EkUe4SSsVPxkSvaJQJ5rqlDphWB2TqYKc61AYkrG7B+qOkJZ3FabxVaY/GIg2y1bwCN6R+e30gCYWQ0cz5TCRqLqvGz/AsxkESVtkVj2xQHOBN+cKSaEJ3NCsYanfag+5HZLYgFOfCA=="
-}</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
